--- a/doc/PixiePico_Pin_Assignment.xlsx
+++ b/doc/PixiePico_Pin_Assignment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/PCOLLA/Documents/GitHub/PixiePico/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1599A80-390D-EF40-A430-842063D6D185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30F39CB-5C1A-3B41-9764-786377C934E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="880" windowWidth="27640" windowHeight="15600" xr2:uid="{76858976-020E-E444-B875-0541BBF74B55}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="66">
   <si>
     <t>GPIO1</t>
   </si>
@@ -212,6 +212,27 @@
   </si>
   <si>
     <t>+3V3</t>
+  </si>
+  <si>
+    <t>PTT</t>
+  </si>
+  <si>
+    <t>DDS</t>
+  </si>
+  <si>
+    <t>SDA0</t>
+  </si>
+  <si>
+    <t>SCL0</t>
+  </si>
+  <si>
+    <t>ROT1</t>
+  </si>
+  <si>
+    <t>ROT2</t>
+  </si>
+  <si>
+    <t>KEYER</t>
   </si>
 </sst>
 </file>
@@ -404,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -477,9 +498,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -854,8 +872,8 @@
   <cols>
     <col min="2" max="2" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -888,7 +906,9 @@
       <c r="E3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="9"/>
+      <c r="F3" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="6">
@@ -901,7 +921,9 @@
       <c r="E4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="9"/>
+      <c r="F4" s="12" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="6">
@@ -928,7 +950,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.2">
@@ -944,7 +966,9 @@
       <c r="E7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="9"/>
+      <c r="F7" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" s="6">
@@ -959,7 +983,9 @@
       <c r="E8" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="9"/>
+      <c r="F8" s="12" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="6">
@@ -974,7 +1000,9 @@
       <c r="E9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="9"/>
+      <c r="F9" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="6">
@@ -1000,7 +1028,9 @@
       <c r="E11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="9"/>
+      <c r="F11" s="12" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="6">
@@ -1045,9 +1075,7 @@
       <c r="E14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="12" t="s">
-        <v>34</v>
-      </c>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B15" s="6">
@@ -1143,7 +1171,7 @@
         <v>14</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
@@ -1290,7 +1318,7 @@
       <c r="E34" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="28"/>
+      <c r="F34" s="9"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="6">

--- a/doc/PixiePico_Pin_Assignment.xlsx
+++ b/doc/PixiePico_Pin_Assignment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/PCOLLA/Documents/GitHub/PixiePico/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30F39CB-5C1A-3B41-9764-786377C934E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194D31A8-B93E-954A-9C47-1B3050435341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="880" windowWidth="27640" windowHeight="15600" xr2:uid="{76858976-020E-E444-B875-0541BBF74B55}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="66">
   <si>
     <t>GPIO1</t>
   </si>
@@ -1129,9 +1129,7 @@
       <c r="E18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="12" t="s">
-        <v>39</v>
-      </c>
+      <c r="F18" s="9"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19" s="6">
@@ -1144,9 +1142,7 @@
       <c r="E19" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>38</v>
-      </c>
+      <c r="F19" s="9"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="6">

--- a/doc/PixiePico_Pin_Assignment.xlsx
+++ b/doc/PixiePico_Pin_Assignment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/PCOLLA/Documents/GitHub/PixiePico/doc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\github\PixiePico\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194D31A8-B93E-954A-9C47-1B3050435341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8070542D-C912-4C02-9B86-A095D3B1BCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="880" windowWidth="27640" windowHeight="15600" xr2:uid="{76858976-020E-E444-B875-0541BBF74B55}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{76858976-020E-E444-B875-0541BBF74B55}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -30,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
   <si>
     <t>GPIO1</t>
   </si>
@@ -226,13 +229,25 @@
     <t>SCL0</t>
   </si>
   <si>
-    <t>ROT1</t>
-  </si>
-  <si>
-    <t>ROT2</t>
-  </si>
-  <si>
     <t>KEYER</t>
+  </si>
+  <si>
+    <t>Usage</t>
+  </si>
+  <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>CLK(A)</t>
+  </si>
+  <si>
+    <t>Rotary</t>
+  </si>
+  <si>
+    <t>DT(B)</t>
+  </si>
+  <si>
+    <t>GPIO29</t>
   </si>
 </sst>
 </file>
@@ -306,7 +321,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -421,11 +436,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -498,6 +524,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -521,13 +568,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
@@ -571,9 +618,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -611,7 +658,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -717,7 +764,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -859,7 +906,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -867,18 +914,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{865F6F77-3EB0-2640-BE53-DD0B4217A0B3}">
-  <dimension ref="B1:G45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:H46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.33203125" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:7" ht="16" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>47</v>
       </c>
@@ -891,11 +939,14 @@
       <c r="E2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="6">
         <v>1</v>
       </c>
@@ -906,11 +957,14 @@
       <c r="E3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" s="6">
         <v>2</v>
       </c>
@@ -921,11 +975,14 @@
       <c r="E4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="6">
         <v>3</v>
       </c>
@@ -934,9 +991,10 @@
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F5" s="30"/>
+      <c r="G5" s="9"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B6" s="6">
         <v>4</v>
       </c>
@@ -949,11 +1007,12 @@
       <c r="E6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="29"/>
+      <c r="G6" s="12" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="6">
         <v>5</v>
       </c>
@@ -966,11 +1025,10 @@
       <c r="E7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F7" s="29"/>
+      <c r="G7" s="34"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="6">
         <v>6</v>
       </c>
@@ -983,11 +1041,10 @@
       <c r="E8" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F8" s="29"/>
+      <c r="G8" s="34"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="6">
         <v>7</v>
       </c>
@@ -1000,11 +1057,12 @@
       <c r="E9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F9" s="29"/>
+      <c r="G9" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="6">
         <v>8</v>
       </c>
@@ -1013,9 +1071,10 @@
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="10"/>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F10" s="30"/>
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="6">
         <v>9</v>
       </c>
@@ -1028,11 +1087,12 @@
       <c r="E11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="29"/>
+      <c r="G11" s="12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="6">
         <v>10</v>
       </c>
@@ -1045,9 +1105,10 @@
       <c r="E12" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F12" s="29"/>
+      <c r="G12" s="9"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="6">
         <v>11</v>
       </c>
@@ -1060,9 +1121,10 @@
       <c r="E13" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F13" s="29"/>
+      <c r="G13" s="9"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="6">
         <v>12</v>
       </c>
@@ -1075,9 +1137,10 @@
       <c r="E14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F14" s="29"/>
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B15" s="6">
         <v>13</v>
       </c>
@@ -1086,9 +1149,10 @@
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F15" s="30"/>
+      <c r="G15" s="9"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B16" s="6">
         <v>14</v>
       </c>
@@ -1101,9 +1165,10 @@
       <c r="E16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="9"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F16" s="29"/>
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B17" s="6">
         <v>15</v>
       </c>
@@ -1116,9 +1181,10 @@
       <c r="E17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F17" s="29"/>
+      <c r="G17" s="9"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B18" s="6">
         <v>16</v>
       </c>
@@ -1129,9 +1195,10 @@
       <c r="E18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="9"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F18" s="29"/>
+      <c r="G18" s="9"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B19" s="6">
         <v>17</v>
       </c>
@@ -1142,9 +1209,10 @@
       <c r="E19" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F19" s="29"/>
+      <c r="G19" s="9"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B20" s="6">
         <v>18</v>
       </c>
@@ -1153,9 +1221,10 @@
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="10"/>
-      <c r="F20" s="9"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F20" s="30"/>
+      <c r="G20" s="9"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B21" s="6">
         <v>19</v>
       </c>
@@ -1166,11 +1235,12 @@
       <c r="E21" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="29"/>
+      <c r="G21" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B22" s="6">
         <v>20</v>
       </c>
@@ -1183,17 +1253,19 @@
       <c r="E22" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="9"/>
-    </row>
-    <row r="23" spans="2:7" ht="4" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F22" s="31"/>
+      <c r="G22" s="9"/>
+    </row>
+    <row r="23" spans="2:8" ht="4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="6"/>
       <c r="C23" s="10"/>
       <c r="D23" s="14"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F23" s="30"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B24" s="6">
         <v>21</v>
       </c>
@@ -1204,9 +1276,10 @@
         <v>39</v>
       </c>
       <c r="E24" s="16"/>
-      <c r="F24" s="9"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F24" s="31"/>
+      <c r="G24" s="9"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B25" s="6">
         <v>22</v>
       </c>
@@ -1217,18 +1290,20 @@
         <v>38</v>
       </c>
       <c r="E25" s="16"/>
-      <c r="F25" s="9"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F25" s="31"/>
+      <c r="G25" s="9"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B26" s="6">
         <v>23</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="8"/>
       <c r="E26" s="16"/>
-      <c r="F26" s="9"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F26" s="31"/>
+      <c r="G26" s="9"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B27" s="6">
         <v>24</v>
       </c>
@@ -1237,9 +1312,10 @@
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="16"/>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F27" s="31"/>
+      <c r="G27" s="9"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B28" s="6">
         <v>25</v>
       </c>
@@ -1248,9 +1324,10 @@
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="16"/>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F28" s="31"/>
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B29" s="6">
         <v>26</v>
       </c>
@@ -1259,9 +1336,10 @@
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="16"/>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F29" s="31"/>
+      <c r="G29" s="9"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B30" s="6">
         <v>27</v>
       </c>
@@ -1270,18 +1348,20 @@
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="16"/>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F30" s="31"/>
+      <c r="G30" s="9"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B31" s="6">
         <v>28</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="8"/>
       <c r="E31" s="16"/>
-      <c r="F31" s="9"/>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F31" s="31"/>
+      <c r="G31" s="9"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B32" s="6">
         <v>29</v>
       </c>
@@ -1290,9 +1370,10 @@
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="16"/>
-      <c r="F32" s="9"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F32" s="31"/>
+      <c r="G32" s="9"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="6">
         <v>30</v>
       </c>
@@ -1301,9 +1382,10 @@
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="16"/>
-      <c r="F33" s="9"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F33" s="31"/>
+      <c r="G33" s="9"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="6">
         <v>31</v>
       </c>
@@ -1314,9 +1396,10 @@
       <c r="E34" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="9"/>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="F34" s="31"/>
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="6">
         <v>32</v>
       </c>
@@ -1329,137 +1412,168 @@
       <c r="E35" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G35" s="17" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B36" s="6">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B36" s="6"/>
+      <c r="C36" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="13"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B37" s="6">
         <v>33</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C37" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="8"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="9"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="6">
+      <c r="D37" s="8"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="9"/>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B38" s="6">
         <v>34</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C38" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="8"/>
+      <c r="E38" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D37" s="8"/>
-      <c r="E37" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="9"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B38" s="6">
+      <c r="F38" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B39" s="6">
         <v>35</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C39" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="9"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B39" s="6">
+      <c r="D39" s="8"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="9"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B40" s="6">
         <v>36</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C40" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D40" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E39" s="10"/>
-      <c r="F39" s="9"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B40" s="6">
+      <c r="E40" s="10"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="9"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B41" s="6">
         <v>37</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C41" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D40" s="8"/>
-      <c r="E40" s="19" t="s">
+      <c r="D41" s="8"/>
+      <c r="E41" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F40" s="9"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B41" s="6">
+      <c r="F41" s="32"/>
+      <c r="G41" s="9"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B42" s="6">
         <v>38</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C42" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D42" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E42" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F41" s="27" t="s">
+      <c r="F42" s="29"/>
+      <c r="G42" s="27" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B42" s="6">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B43" s="6">
         <v>39</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C43" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="8"/>
-      <c r="E42" s="19" t="s">
+      <c r="D43" s="8"/>
+      <c r="E43" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F42" s="26" t="s">
+      <c r="F43" s="32"/>
+      <c r="G43" s="26" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B43" s="6">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B44" s="6">
         <v>40</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C44" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D44" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="E43" s="10"/>
-      <c r="F43" s="9"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B44" s="20"/>
-      <c r="C44" s="16" t="s">
+      <c r="E44" s="10"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="9"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B45" s="20"/>
+      <c r="C45" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="16" t="s">
+      <c r="D45" s="8"/>
+      <c r="E45" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F45" s="31"/>
+      <c r="G45" s="9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="2:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="21"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="24" t="s">
+    <row r="46" spans="2:7" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="21"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="F45" s="25" t="s">
+      <c r="F46" s="33"/>
+      <c r="G46" s="25" t="s">
         <v>44</v>
       </c>
     </row>

--- a/doc/PixiePico_Pin_Assignment.xlsx
+++ b/doc/PixiePico_Pin_Assignment.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\github\PixiePico\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8070542D-C912-4C02-9B86-A095D3B1BCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088620AD-2E75-4158-82B6-6C383B41B819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{76858976-020E-E444-B875-0541BBF74B55}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="75">
   <si>
     <t>GPIO1</t>
   </si>
@@ -241,13 +242,28 @@
     <t>CLK(A)</t>
   </si>
   <si>
-    <t>Rotary</t>
-  </si>
-  <si>
     <t>DT(B)</t>
   </si>
   <si>
     <t>GPIO29</t>
+  </si>
+  <si>
+    <t>AF In</t>
+  </si>
+  <si>
+    <t>MENU</t>
+  </si>
+  <si>
+    <t>(out)</t>
+  </si>
+  <si>
+    <t>(in)</t>
+  </si>
+  <si>
+    <t>Encoder SW</t>
+  </si>
+  <si>
+    <t>Encoder</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1023,9 @@
       <c r="E6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="29"/>
+      <c r="F6" s="29" t="s">
+        <v>71</v>
+      </c>
       <c r="G6" s="12" t="s">
         <v>59</v>
       </c>
@@ -1057,7 +1075,9 @@
       <c r="E9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="29"/>
+      <c r="F9" s="29" t="s">
+        <v>72</v>
+      </c>
       <c r="G9" s="12" t="s">
         <v>63</v>
       </c>
@@ -1087,7 +1107,9 @@
       <c r="E11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="29"/>
+      <c r="F11" s="29" t="s">
+        <v>71</v>
+      </c>
       <c r="G11" s="12" t="s">
         <v>43</v>
       </c>
@@ -1235,7 +1257,9 @@
       <c r="E21" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="29"/>
+      <c r="F21" s="29" t="s">
+        <v>71</v>
+      </c>
       <c r="G21" s="12" t="s">
         <v>60</v>
       </c>
@@ -1396,8 +1420,12 @@
       <c r="E34" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="31"/>
-      <c r="G34" s="9"/>
+      <c r="F34" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="6">
@@ -1413,10 +1441,10 @@
         <v>24</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="G35" s="17" t="s">
-        <v>42</v>
+        <v>73</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.35">
@@ -1427,10 +1455,10 @@
       <c r="D36" s="13"/>
       <c r="E36" s="7"/>
       <c r="F36" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="G36" s="12" t="s">
         <v>67</v>
-      </c>
-      <c r="G36" s="12" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -1450,14 +1478,14 @@
         <v>34</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G38" s="12" t="s">
         <v>66</v>
